--- a/outputs/lbg-2025/LloydsBankingGroup_2025_Board_Governance_deepseek.xlsx
+++ b/outputs/lbg-2025/LloydsBankingGroup_2025_Board_Governance_deepseek.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -602,93 +602,93 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>% Women on Board</t>
+          <t>Director Names</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>Robin Budenberg, Charlie Nunn, William Chalmers, Cathy Turner, Nathan Bostock, Sarah Legg, Amanda Mackenzie, Harmeen Mehta, Chris Vogelzang, Scott Wheway, Catherine Woods</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>% Independent Directors</t>
+          <t>% Women on Board</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Average Director Age</t>
+          <t>% Independent Directors</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Average Tenure (years)</t>
+          <t>Average Director Age</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Average Tenure (years)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Board Inclusion Policy: commitment to maintain at least four women board members and 45-55% female representation; Parker Review recommendation for at least one Black, Asian or Minority Ethnic board member.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>The Board has a Board Inclusion Policy, with a commitment to at least 40% women (currently 50%) and at least one Black, Asian or Minority Ethnic Board member (currently two). The Board also meets UK Listing Rule diversity targets. The Board performance review is externally facilitated every three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Post-Election Projected Board</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CEO and Chair Separated</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="B16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Board Evaluation Disclosed</t>
+          <t>CEO and Chair Separated</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -700,125 +700,149 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Voting Standard for Directors</t>
+          <t>Board Evaluation Disclosed</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Board Size</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>11</v>
+          <t>Voting Standard for Directors</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Executive Directors</t>
+          <t>Board Size</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Non-Executive Directors</t>
+          <t>Executive Directors</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Independent Directors</t>
+          <t>Non-Executive Directors</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>% Women on Board</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
+          <t>Independent Directors</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>% Independent Directors</t>
+          <t>Director Names</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>Robin Budenberg, Charlie Nunn, William Chalmers, Cathy Turner, Nathan Bostock, Sarah Legg, Amanda Mackenzie, Harmeen Mehta, Chris Vogelzang, Scott Wheway, Catherine Woods</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Average Director Age</t>
+          <t>% Women on Board</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Average Tenure (years)</t>
+          <t>% Independent Directors</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Average Director Age</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Average Tenure (years)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
-        </is>
-      </c>
+      <c r="B29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+      <c r="A30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -843,7 +867,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="37" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
@@ -948,13 +972,11 @@
       <c r="E2" s="6" t="n">
         <v>2020</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>5</v>
-      </c>
+      <c r="F2" s="6" t="n"/>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -1008,13 +1030,11 @@
       <c r="E3" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr"/>
@@ -1060,13 +1080,11 @@
       <c r="E4" s="8" t="n">
         <v>2019</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>6</v>
-      </c>
+      <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr"/>
@@ -1112,18 +1130,16 @@
       <c r="E5" s="9" t="n">
         <v>2022</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Nomination and Governance Committee; Board Risk Committee; Remuneration Committee</t>
+          <t>Board Risk Committee; Remuneration Committee; Nomination and Governance Committee</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -1172,13 +1188,11 @@
       <c r="E6" s="10" t="n">
         <v>2024</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1228,13 +1242,11 @@
       <c r="E7" s="9" t="n">
         <v>2019</v>
       </c>
-      <c r="F7" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1288,18 +1300,16 @@
       <c r="E8" s="10" t="n">
         <v>2018</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Audit Committee; Nomination and Governance Committee; Remuneration Committee; Responsible Business Committee</t>
+          <t>Audit Committee; Remuneration Committee; Nomination and Governance Committee; Responsible Business Committee</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
@@ -1348,13 +1358,11 @@
       <c r="E9" s="9" t="n">
         <v>2021</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr"/>
@@ -1400,13 +1408,11 @@
       <c r="E10" s="10" t="n">
         <v>2025</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -1456,20 +1462,18 @@
       <c r="E11" s="9" t="n">
         <v>2022</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
         <v>2025</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Stepped down on 31 October 2025</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Nomination and Governance Committee; Board Risk Committee</t>
+          <t>Board Risk Committee; Nomination and Governance Committee</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr"/>
@@ -1514,13 +1518,11 @@
       <c r="E12" s="10" t="n">
         <v>2020</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>5</v>
-      </c>
+      <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>In role at year end</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -1556,7 +1558,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -1633,11 +1635,15 @@
       </c>
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F2" s="6" t="n"/>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Chair of Lloyds Banking Group plc. Formerly Chair of The Crown Estate, spent 25 years at S.G. Warburg/UBS, former CEO and Chairman of UK Financial Investments. Qualified chartered accountant.</t>
+          <t>Robin was Chair of The Crown Estate for nine years until July 2025. He spent 25 years advising UK companies and the UK Government while working for S.G. Warburg/UBS Investment Bank and was formerly Chief Executive and Chairman of UK Financial Investments (UKFI), managing the Government’s investments in UK banks following the 2008 financial crisis. He qualified as a chartered accountant.</t>
         </is>
       </c>
     </row>
@@ -1650,11 +1656,15 @@
       <c r="B3" s="8" t="n"/>
       <c r="C3" s="8" t="n"/>
       <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Group Chief Executive. Over 25 years in financial services, previously at HSBC including Global Chief Executive Wealth and Personal Banking, and at Accenture and McKinsey.</t>
+          <t>Charlie has over 25 years’ experience in the financial services sector. Prior to joining the Group, Charlie held a range of leadership positions at HSBC, including Global Chief Executive, Wealth and Personal Banking, and Group Head of Wealth Management and Digital, as well as Global Chief Operating Officer of Retail Banking and Wealth Management. Charlie began his career at Accenture, where he worked for 13 years in the US, France, Switzerland and the UK before being made a Partner. He then moved to McKinsey &amp; Co. as a Senior Partner, leading on projects for five years.</t>
         </is>
       </c>
     </row>
@@ -1667,11 +1677,15 @@
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Chief Financial Officer. Over 25 years in financial services, previously senior roles at Morgan Stanley and J.P. Morgan.</t>
+          <t>William has worked in financial services for over 25 years and previously held a number of senior roles at Morgan Stanley, including Co-Head of the Global Financial Institutions Group and Head of EMEA Financial Institutions Group. Before joining Morgan Stanley, William worked for J. P. Morgan, again in the Financial Institutions Group.</t>
         </is>
       </c>
     </row>
@@ -1684,11 +1698,15 @@
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Senior Independent Director. Significant financial services experience, previously senior executive at Barclays and other boards.</t>
+          <t>Cathy has significant financial services experience, having worked in senior executive positions at Barclays plc and at the Group. Cathy has previously been a Non-Executive Director and Chair of the Remuneration Committee of Aldermore Group plc, Quilter plc, Spectris plc and Countrywide plc.</t>
         </is>
       </c>
     </row>
@@ -1701,11 +1719,15 @@
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Independent non-executive director. Former CEO Santander UK, former CFO and CRO at RBS. Chartered accountant.</t>
+          <t>Nathan was Chief Executive Officer of Santander UK plc from 2014 until 2022 and then Head of Investment Platforms at Banco Santander S.A. until his retirement from Santander in 2023. Prior to joining Santander in 2014, Nathan was an executive director and Group Chief Financial Officer of RBS and previously held the post of Chief Risk Officer at RBS. Before joining RBS, Nathan held various senior positions at Santander UK plc between 2004 and 2009, including Executive Director, Finance Director and commercial Chief Executive Officer roles in Financial Markets and Corporate Banking and in Cards and Insurance. He is qualified as a chartered accountant.</t>
         </is>
       </c>
     </row>
@@ -1718,11 +1740,15 @@
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Chair of Audit Committee. Almost 30 years at HSBC, including Group Financial Controller and CFO Asia Pacific. FCMA, FCT.</t>
+          <t>Sarah has spent her entire executive career in financial services with almost 30 years at HSBC. She was the Group Financial Controller, a Group General Manager and CFO for HSBC’s Asia Pacific region. She also spent eight years as a Non-Executive Director of Hang Seng Bank Limited.</t>
         </is>
       </c>
     </row>
@@ -1739,11 +1765,15 @@
       </c>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Chair of Responsible Business Committee. Former CEO of Business in the Community, former Aviva Group Executive. Extensive ESG experience.</t>
+          <t>Amanda was Chief Executive of Business in the Community, of which King Charles III is the Royal Founding Patron and which promotes responsible business and corporate responsibility. Prior to that role, she was a member of Aviva’s Group Executive for seven years as Chief Marketing and Communications Officer and was seconded to help launch the United Nations Sustainable Development Goals. She is also a former Director of British Airways AirMiles, BT, Hewlett Packard Inc and British Gas.</t>
         </is>
       </c>
     </row>
@@ -1756,11 +1786,15 @@
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Chief Digital and Innovation Officer at BT. Previously Global CIO at Bharti Airtel, CIO at BBVA, HSBC, Bank of America Merrill Lynch.</t>
+          <t>Harmeen was appointed Chief Digital and Innovation Officer at Equinix in April 2025. Prior to that role, she was Chief Digital and Innovation Officer at BT and spent seven years as Global Chief Information Officer and Head of Cyber Security and Cloud Business at Bharti Airtel, leading its cloud and security businesses. Earlier in her career, Harmeen held CIO positions at BBVA, HSBC and Bank of America Merrill Lynch.</t>
         </is>
       </c>
     </row>
@@ -1773,11 +1807,15 @@
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Appointed June 2025. Former CEO Danske Bank, senior positions at ABN AMRO. Extensive retail and commercial banking experience.</t>
+          <t>Chris was Chief Executive Officer of Danske Bank A/S from 2019 until 2021. Prior to that, he held a number of senior positions at ABN AMRO, including Managing Board member with responsibility for Retail and Private Banking, Chief Executive Officer of Retail Banking for The Netherlands and Chief Executive Officer of Global Private Banking.</t>
         </is>
       </c>
     </row>
@@ -1790,11 +1828,15 @@
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Retired October 2025. Former Chair of Centrica, AXA UK, Aviva Insurance. Executive experience in retail (Best Buy, Boots, Tesco).</t>
+          <t>Scott was a Non-Executive Director of Centrica plc between 2016 and 2020 and served as Chair of Centrica plc between 2020 and 2024. He was formerly Chair of AXA UK plc, Chair of Aviva Insurance Limited, a Non-Executive Director of Aviva plc and Senior Independent Director of Santander UK plc. He worked as an executive in the retail sector for over 25 years where he held positions including chief executive officer of Best Buy Europe, managing director of Boots the Chemist plc and a number of senior executive positions at Tesco plc.</t>
         </is>
       </c>
     </row>
@@ -1807,11 +1849,15 @@
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Chair of Board Risk Committee. Former Deputy Chair and SID of AIB Group. Executive career at J.P. Morgan.</t>
+          <t>Catherine is a former Deputy Chair and Senior Independent Director of AIB Group plc where she also chaired the Board Audit Committee. In her executive career with J.P. Morgan Securities, she was Vice President, European Financial Institutions, Mergers and Acquisitions, and Vice President Equity Research Department, forming the European Banks Team.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1867,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2344,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2655,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -2705,14 +2751,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2778,7 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -2851,7 +2897,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Responsible Business Committee</t>
+          <t>Nomination and Governance Committee; Remuneration Committee; Responsible Business Committee</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -2939,7 +2985,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Independent non-executive director and Chair of Lloyds Bank Corporate Markets plc</t>
+          <t>Independent non-executive director</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -3063,7 +3109,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Audit Committee; Board Risk Committee; Remuneration Committee; Responsible Business Committee</t>
+          <t>Audit Committee; Board Risk Committee; Responsible Business Committee</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -3121,7 +3167,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Audit Committee; Nomination and Governance Committee; Remuneration Committee; Responsible Business Committee</t>
+          <t>Responsible Business Committee; Audit Committee; Remuneration Committee; Nomination and Governance Committee</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -3229,7 +3275,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Board Risk Committee; Nomination and Governance Committee; Remuneration Committee</t>
+          <t>Remuneration Committee; Board Risk Committee; Nomination and Governance Committee</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -3267,7 +3313,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Independent non-executive director and Chair of Scottish Widows Group</t>
+          <t>Independent non-executive director</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -3287,7 +3333,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Board Risk Committee; Nomination and Governance Committee</t>
+          <t>Nomination and Governance Committee; Board Risk Committee</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr"/>
@@ -3341,7 +3387,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Audit Committee; Board Risk Committee; Remuneration Committee</t>
+          <t>Board Risk Committee; Audit Committee; Remuneration Committee</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -3372,7 +3418,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-16  |  Provider: deepseek / deepseek-v4-flash</t>
+          <t>Source: /home/cop98/dev/board-governance-extractor/data/2025-lbg-annual-report.pdf | /home/cop98/dev/board-governance-extractor/data/2025-lbg-notice-of-agm.pdf  |  Extracted: 2026-05-18  |  Provider: deepseek / deepseek-v4-flash</t>
         </is>
       </c>
     </row>
